--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEW_YORK_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEW_YORK_2020.xlsx
@@ -1795,7 +1795,7 @@
         <v>17</v>
       </c>
       <c r="D80">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="81">
@@ -1831,7 +1831,7 @@
         <v>173</v>
       </c>
       <c r="D82">
-        <v>0.009310085028522225</v>
+        <v>0.009310085028522224</v>
       </c>
     </row>
     <row r="83">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C101">
@@ -2371,7 +2371,7 @@
         <v>18</v>
       </c>
       <c r="D112">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="113">
@@ -2749,7 +2749,7 @@
         <v>18</v>
       </c>
       <c r="D133">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="134">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C182">
@@ -3703,7 +3703,7 @@
         <v>18</v>
       </c>
       <c r="D186">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="187">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C188">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C195">
@@ -4225,7 +4225,7 @@
         <v>18</v>
       </c>
       <c r="D215">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="216">
@@ -4369,7 +4369,7 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="224">
@@ -5179,7 +5179,7 @@
         <v>17</v>
       </c>
       <c r="D268">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="269">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C273">
@@ -5341,7 +5341,7 @@
         <v>18</v>
       </c>
       <c r="D277">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="278">
@@ -6205,7 +6205,7 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="326">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C337">
@@ -8221,7 +8221,7 @@
         <v>18</v>
       </c>
       <c r="D437">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="438">
@@ -9265,7 +9265,7 @@
         <v>17</v>
       </c>
       <c r="D495">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="496">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C512">
@@ -10111,7 +10111,7 @@
         <v>18</v>
       </c>
       <c r="D542">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="543">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C561">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C606">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C679">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Yutanduchi De Guerero</t>
+          <t>Yutanduchi De Guerrero</t>
         </is>
       </c>
       <c r="C700">
@@ -13027,7 +13027,7 @@
         <v>18</v>
       </c>
       <c r="D704">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="705">
@@ -13045,7 +13045,7 @@
         <v>18</v>
       </c>
       <c r="D705">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="706">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C727">
@@ -13657,7 +13657,7 @@
         <v>17</v>
       </c>
       <c r="D739">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="740">
@@ -14179,7 +14179,7 @@
         <v>18</v>
       </c>
       <c r="D768">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="769">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C779">
@@ -14791,7 +14791,7 @@
         <v>18</v>
       </c>
       <c r="D802">
-        <v>0.0009686793671294801</v>
+        <v>0.00096867936712948</v>
       </c>
     </row>
     <row r="803">
@@ -15367,7 +15367,7 @@
         <v>17</v>
       </c>
       <c r="D834">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="835">
@@ -15709,7 +15709,7 @@
         <v>17</v>
       </c>
       <c r="D853">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="854">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Totoltepec De Guerero</t>
+          <t>Totoltepec De Guerrero</t>
         </is>
       </c>
       <c r="C877">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C882">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Amaxac De Guerero</t>
+          <t>Amaxac De Guerrero</t>
         </is>
       </c>
       <c r="C971">
@@ -19741,7 +19741,7 @@
         <v>17</v>
       </c>
       <c r="D1077">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="1078">
@@ -19903,7 +19903,7 @@
         <v>17</v>
       </c>
       <c r="D1086">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="1087">
@@ -20101,7 +20101,7 @@
         <v>17</v>
       </c>
       <c r="D1097">
-        <v>0.0009148638467333979</v>
+        <v>0.000914863846733398</v>
       </c>
     </row>
     <row r="1098">
